--- a/dataset/out/00-rfx/03_Vendor_Questionnaire.xlsx
+++ b/dataset/out/00-rfx/03_Vendor_Questionnaire.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Northbridge Retail India Pvt Ltd  |  Return with your commercial offer.</t>
+          <t>Kaveri Retail India Pvt Ltd  |  Return with your commercial offer.</t>
         </is>
       </c>
     </row>
